--- a/artfynd/A 29128-2025 artfynd.xlsx
+++ b/artfynd/A 29128-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131155590</v>
       </c>
       <c r="B2" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131155723</v>
       </c>
       <c r="B3" t="n">
-        <v>57876</v>
+        <v>57878</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29128-2025 artfynd.xlsx
+++ b/artfynd/A 29128-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131155590</v>
       </c>
       <c r="B2" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131155723</v>
       </c>
       <c r="B3" t="n">
-        <v>57878</v>
+        <v>57879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29128-2025 artfynd.xlsx
+++ b/artfynd/A 29128-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>131155723</v>
       </c>
       <c r="B3" t="n">
-        <v>57879</v>
+        <v>57880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29128-2025 artfynd.xlsx
+++ b/artfynd/A 29128-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131155590</v>
       </c>
       <c r="B2" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131155723</v>
       </c>
       <c r="B3" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29128-2025 artfynd.xlsx
+++ b/artfynd/A 29128-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131155590</v>
       </c>
       <c r="B2" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131155723</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29128-2025 artfynd.xlsx
+++ b/artfynd/A 29128-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131155590</v>
       </c>
       <c r="B2" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131155723</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>57890</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29128-2025 artfynd.xlsx
+++ b/artfynd/A 29128-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131155590</v>
+        <v>131155723</v>
       </c>
       <c r="B2" t="n">
-        <v>57086</v>
+        <v>57945</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100110</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -716,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574144</v>
+        <v>574125</v>
       </c>
       <c r="R2" t="n">
-        <v>6697441</v>
+        <v>6697629</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,9 +753,24 @@
           <t>2025-04-24</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>En till gråspett. Sjunger mer frekvent. Kanske en ny individ.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131155723</v>
+        <v>131155590</v>
       </c>
       <c r="B3" t="n">
-        <v>57890</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,31 +812,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100110</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -827,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574125</v>
+        <v>574144</v>
       </c>
       <c r="R3" t="n">
-        <v>6697629</v>
+        <v>6697441</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,24 +875,9 @@
           <t>2025-04-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>En till gråspett. Sjunger mer frekvent. Kanske en ny individ.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 29128-2025 artfynd.xlsx
+++ b/artfynd/A 29128-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
           <t>Fågelinventering Hålsberget 2024-2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131155723</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,8 +915,17 @@
           <t>Fågelinventering Hålsberget 2024-2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131155590</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>